--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260813.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260813.xlsx
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,872,788</t>
+          <t>2,196,162</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>2,196,162</t>
+          <t>1,872,788</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>217,179,758</t>
+          <t>17,808,090</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>17,808,090</t>
+          <t>217,179,758</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>251,642,020</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>251,642,020</t>
+          <t>5,005,548</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>5,005,548</t>
+          <t>648</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
